--- a/ONTOPRIVACY/03_CATALOGO/CATALOGO_ONTOPRIVACY_v2.xlsx
+++ b/ONTOPRIVACY/03_CATALOGO/CATALOGO_ONTOPRIVACY_v2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985FB057-804C-4249-BE95-8B25E192A730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumo" sheetId="1" r:id="rId1"/>
